--- a/cp-ins-iti-105/ig/all-profiles.xlsx
+++ b/cp-ins-iti-105/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:04:23+00:00</t>
+    <t>2026-10-15T15:21:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3843,6 +3843,10 @@
     <t>https://profiles.ihe.net/ITI/MHD/StructureDefinition/IHE.MHD.SimplifiedPublish.DocumentReference</t>
   </si>
   <si>
+    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}constr-sp-subject-sourcePatientInfo-ins:Lorsque subject.identifier porte un matricule INS et que context.sourcePatientInfo est fourni, la ressource Patient contenue référencée par context.sourcePatientInfo doit porter le même matricule INS (même system et même value). {(subject.identifier.where(system in ('urn:oid:1.2.250.1.213.1.4.8' | 'urn:oid:1.2.250.1.213.1.4.9' | 'urn:oid:1.2.250.1.213.1.4.10' | 'urn:oid:1.2.250.1.213.1.4.11')).exists() and context.sourcePatientInfo.exists()) implies contained.ofType(Patient).where(('#' + id) = %resource.context.sourcePatientInfo.reference).identifier.where(system = %resource.subject.identifier.system and value = %resource.subject.identifier.value).exists()}</t>
+  </si>
+  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
@@ -3858,7 +3862,7 @@
     <t>Kind of document (LOINC if possible)</t>
   </si>
   <si>
-    <t>Patient concerné par ce document. La ressource référencée peut être présente sous l’élément DocumentReference.contained ou via le champ identifier.</t>
+    <t>Patient titulaire du dossier dans le système cible. Lorsque le patient dispose d'une identité INS qualifiée, le matricule INS est porté par subject.identifier (référence logique, admise par IHE MHD ITI-105 §2:3.105.4.1.2.2 pour un identifiant national). La référence peut aussi pointer une ressource Patient déjà connue du système cible. Conformément à IHE MHD, la ressource Patient n'est pas contenue (contained) : les traits du patient tels que connus du producteur sont portés par context.sourcePatientInfo. Lorsque context.sourcePatientInfo est fourni, son matricule INS doit être identique à celui de subject.identifier (invariant constr-sp-subject-sourcePatientInfo-ins) ; en cas de discordance, la transaction est rejetée.</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|Device|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person)
@@ -3912,10 +3916,6 @@
   </si>
   <si>
     <t>Référence vers la ressource Patient titulaire du dossier. Conformément à IHE MHD ITI-105, lorsque fournie, cette référence pointe une ressource Patient contenue (contained). Selon le statut d'identité, la ressource est conforme au profil FR Core Patient (identité non qualifiée) ou FR Core Patient INS (identité qualifiée, matricule INS + traits INSi) qui hérite de profil FR Core Patient.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-constr-sp-sourcePatientInfo-contained:Lorsqu'il est fourni, context.sourcePatientInfo doit référencer une ressource Patient contenue (contained), cf spécifications IHE MHD ITI-105 §2:3.105.4.1.2.2. {reference.exists() implies reference.startsWith('#')}</t>
   </si>
   <si>
     <t>pdsm-submissionset-comprehensive</t>
@@ -71075,7 +71075,7 @@
         <v>75</v>
       </c>
       <c r="AK625" t="s" s="2">
-        <v>82</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="626">
@@ -72581,7 +72581,7 @@
         <v>105</v>
       </c>
       <c r="N640" t="s" s="2">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="O640" t="s" s="2">
         <v>107</v>
@@ -73013,7 +73013,7 @@
         <v>75</v>
       </c>
       <c r="T644" t="s" s="2">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="U644" t="s" s="2">
         <v>75</v>
@@ -73031,10 +73031,10 @@
         <v>211</v>
       </c>
       <c r="Z644" t="s" s="2">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="AA644" t="s" s="2">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="AB644" t="s" s="2">
         <v>75</v>
@@ -73206,7 +73206,7 @@
         <v>220</v>
       </c>
       <c r="M646" t="s" s="2">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="N646" t="s" s="2">
         <v>221</v>
@@ -73412,7 +73412,7 @@
         <v>234</v>
       </c>
       <c r="M648" t="s" s="2">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="N648" t="s" s="2">
         <v>236</v>
@@ -73617,7 +73617,7 @@
         <v>85</v>
       </c>
       <c r="L650" t="s" s="2">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="M650" t="s" s="2">
         <v>244</v>
@@ -73935,10 +73935,10 @@
         <v>258</v>
       </c>
       <c r="M653" t="s" s="2">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="N653" t="s" s="2">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="O653" t="s" s="2">
         <v>261</v>
@@ -74003,7 +74003,7 @@
         <v>75</v>
       </c>
       <c r="AK653" t="s" s="2">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="654">
@@ -74355,7 +74355,7 @@
         <v>159</v>
       </c>
       <c r="M657" t="s" s="2">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="N657" t="s" s="2">
         <v>273</v>
@@ -74423,7 +74423,7 @@
         <v>75</v>
       </c>
       <c r="AK657" t="s" s="2">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="658">
@@ -74460,7 +74460,7 @@
         <v>278</v>
       </c>
       <c r="M658" t="s" s="2">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="N658" t="s" s="2">
         <v>280</v>
@@ -74526,7 +74526,7 @@
         <v>75</v>
       </c>
       <c r="AK658" t="s" s="2">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="659">
@@ -74563,7 +74563,7 @@
         <v>98</v>
       </c>
       <c r="M659" t="s" s="2">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="N659" t="s" s="2">
         <v>284</v>
@@ -74775,7 +74775,7 @@
         <v>258</v>
       </c>
       <c r="M661" t="s" s="2">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="N661" t="s" s="2">
         <v>295</v>
@@ -75714,7 +75714,7 @@
         <v>320</v>
       </c>
       <c r="M670" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="N670" t="s" s="2">
         <v>322</v>
@@ -75821,7 +75821,7 @@
         <v>327</v>
       </c>
       <c r="M671" t="s" s="2">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="N671" t="s" s="2">
         <v>329</v>
@@ -76247,7 +76247,7 @@
         <v>355</v>
       </c>
       <c r="M675" t="s" s="2">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="N675" t="s" s="2">
         <v>357</v>
@@ -77250,7 +77250,7 @@
         <v>75</v>
       </c>
       <c r="AK684" t="s" s="2">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="685">
@@ -77355,7 +77355,7 @@
         <v>75</v>
       </c>
       <c r="AK685" t="s" s="2">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="686">
@@ -77392,7 +77392,7 @@
         <v>414</v>
       </c>
       <c r="M686" t="s" s="2">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="N686" t="s" s="2">
         <v>416</v>
@@ -77458,7 +77458,7 @@
         <v>75</v>
       </c>
       <c r="AK686" t="s" s="2">
-        <v>1249</v>
+        <v>96</v>
       </c>
     </row>
     <row r="687">
@@ -81052,7 +81052,7 @@
         <v>75</v>
       </c>
       <c r="T721" t="s" s="2">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="U721" t="s" s="2">
         <v>75</v>
